--- a/reports/Debug-purgatory-20260105/Month to Date (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/Month to Date (Actual)_Revenue.xlsx
@@ -73,18 +73,18 @@
     <t>account</t>
   </si>
   <si>
+    <t>T110</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
+    <t>T100</t>
+  </si>
+  <si>
     <t>T103</t>
   </si>
   <si>
-    <t>T110</t>
-  </si>
-  <si>
-    <t>T100</t>
-  </si>
-  <si>
-    <t>T105</t>
-  </si>
-  <si>
     <t>department</t>
   </si>
   <si>
@@ -133,7 +133,7 @@
     <t>D5209</t>
   </si>
   <si>
-    <t xml:space="preserve">D6720                    </t>
+    <t>D6720</t>
   </si>
   <si>
     <t>D6790</t>
@@ -536,7 +536,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="2">
-        <v>300.0000</v>
+        <v>180.0000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -550,7 +550,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="2">
-        <v>180.0000</v>
+        <v>4379.0000</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -578,7 +578,7 @@
         <v>24</v>
       </c>
       <c r="D5" s="2">
-        <v>4379.0000</v>
+        <v>300.0000</v>
       </c>
     </row>
     <row r="6" spans="1:4">
